--- a/documenti/SpaceX_modello.xlsx
+++ b/documenti/SpaceX_modello.xlsx
@@ -346,7 +346,7 @@
     <t xml:space="preserve">... cioe' EV / ricavi 2026E di Starlink</t>
   </si>
   <si>
-    <t xml:space="preserve">contro un paniere telecom di 2,7x</t>
+    <t xml:space="preserve">contro il paniere di Starlink di 2,7x (Iridium, il multiplo piu' alto fra gli operatori con ricavi a regime: 7,5x)</t>
   </si>
   <si>
     <t xml:space="preserve">3. DCF inverso: che cosa deve accadere perche' il valore dei flussi arrivi al prezzo</t>

--- a/documenti/SpaceX_modello.xlsx
+++ b/documenti/SpaceX_modello.xlsx
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="608">
   <si>
     <t xml:space="preserve">SpaceX: il prezzo e il valore. Modello in formule</t>
   </si>
@@ -391,6 +391,39 @@
     <t xml:space="preserve">Ricavi impliciti al prezzo / ricavi di Amazon 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Se l'AI a regime valesse come un hyperscaler: valore finale dell'AI al 2036 ai multipli del paniere (EV/ricavi ed EV/EBITDA) invece del valore di continuazione del DCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valore finale dell'AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI basso (mld)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI alto (mld)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ per azione, basso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ per azione, alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF del modello, tutto a rischio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valore AI: modello Python (prezzo_e_valore.py); $ per azione: formula del ponte sul valore del gruppo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF del modello, solo l'AI con successo certo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multipli del paniere, AI a rischio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multipli del paniere, solo l'AI con successo certo</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. Il confronto: quanta parte del prezzo spiegano i flussi</t>
   </si>
   <si>
@@ -1867,7 +1900,7 @@
     <t xml:space="preserve">Controlli: Excel contro il modello Python</t>
   </si>
   <si>
-    <t xml:space="preserve">Colonna C: risultato del modello di calcolo in Python dell'autore (testo di riferimento, non formula). Colonna D: differenza. Le piccole differenze sul valore per azione vengono dalla linearizzazione dei claim azionari (tarata fra 45 e 90 $: sotto i 20 $, cioe' ai multipli dei panieri, lo scarto sale a 5-6 centesimi).</t>
+    <t xml:space="preserve">Colonna C: risultato del modello di calcolo in Python dell'autore (testo di riferimento, non formula). Colonna D: differenza. Le piccole differenze sul valore per azione vengono dalla linearizzazione dei claim azionari (tarata fra 45 e 90 $: fuori da quell'intervallo, ai multipli dei panieri o con l'AI come un hyperscaler, lo scarto sale a 3-6 centesimi).</t>
   </si>
   <si>
     <t xml:space="preserve">Grandezza</t>
@@ -1940,6 +1973,12 @@
   </si>
   <si>
     <t xml:space="preserve">Quota del prezzo spiegata dai flussi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI come hyperscaler e certa, $ per azione (basso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI come hyperscaler e certa, $ per azione (alto)</t>
   </si>
   <si>
     <t xml:space="preserve">Mediana target consorzio</t>
@@ -2713,7 +2752,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2732,32 +2771,32 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B5" s="15" t="n">
         <f aca="false">B50</f>
@@ -2773,12 +2812,12 @@
       </c>
       <c r="E5" s="45"/>
       <c r="F5" s="3" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">Fisco!$C$38</f>
@@ -2797,12 +2836,12 @@
         <v>0.0367672057050541</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">Finanziamento!$C$15</f>
@@ -2821,12 +2860,12 @@
         <v>0.215202760709261</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">B44</f>
@@ -2845,12 +2884,12 @@
         <v>0.229589119859021</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">Segmenti!$M$38-Segmenti!$L$39</f>
@@ -2869,12 +2908,12 @@
         <v>2.35168176427936</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">Segmenti!$N$38-Segmenti!$M$38</f>
@@ -2893,12 +2932,12 @@
         <v>1.6229635312185</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">Segmenti!$K$38-Segmenti!$N$38</f>
@@ -2917,12 +2956,12 @@
         <v>0.187617326543894</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">B43</f>
@@ -2941,12 +2980,12 @@
         <v>0.290687400335052</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">-B41</f>
@@ -2965,12 +3004,12 @@
         <v>-1.18277440693992</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B14" s="20" t="n">
         <f aca="false">C13</f>
@@ -2983,7 +3022,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B16" s="15" t="n">
         <f aca="false">SUM(B6:B11)</f>
@@ -2992,7 +3031,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">B16/Segmenti!$K$38</f>
@@ -3001,7 +3040,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B18" s="15" t="n">
         <f aca="false">Sinergie!$B$14-B5</f>
@@ -3010,7 +3049,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">LN(Sinergie!$B$14/B5)</f>
@@ -3019,7 +3058,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B20" s="46" t="n">
         <f aca="false">Sinergie!$B$14-(Segmenti!$K$38+B43)</f>
@@ -3028,32 +3067,32 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B24" s="25" t="n">
         <v>0</v>
@@ -3070,12 +3109,12 @@
         <v>66.1027569729127</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B25" s="25" t="n">
         <v>0.015</v>
@@ -3092,12 +3131,12 @@
         <v>52.1801997737398</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B26" s="25" t="n">
         <v>0.3</v>
@@ -3114,12 +3153,12 @@
         <v>51.8159146160159</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B40" s="15" t="n">
         <f aca="false">-(MIN(0,Segmenti!$K$28)+MIN(0,Segmenti!$K$29))</f>
@@ -3128,7 +3167,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B41" s="15" t="n">
         <f aca="false">Input!$B$50*B40</f>
@@ -3137,7 +3176,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B42" s="10" t="n">
         <f aca="false">Blocchi!$Q$150</f>
@@ -3146,7 +3185,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B43" s="15" t="n">
         <f aca="false">Input!$B$49*B42</f>
@@ -3155,7 +3194,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B44" s="15" t="n">
         <f aca="false">Segmenti!$L$39-Segmenti!$L$38</f>
@@ -3164,7 +3203,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3196,7 +3235,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B50" s="15" t="n">
         <f aca="false">SUM(B47:B49)</f>
@@ -3228,7 +3267,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3247,12 +3286,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B4" s="34" t="n">
         <f aca="false">(Tassi!$B$11*MAX(0,Segmenti!$K$14)+Tassi!$C$11*MAX(0,Segmenti!$K$25)+Tassi!$D$11*MAX(0,Segmenti!$K$36))/(MAX(0,Segmenti!$K$14)+MAX(0,Segmenti!$K$25)+MAX(0,Segmenti!$K$36))</f>
@@ -3261,7 +3300,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B5" s="38" t="n">
         <f aca="false">(1-Input!$B$38)*(1+Ponte!$B$4)^Input!$B$34/(Input!$B$35/1000+Input!$B$37)</f>
@@ -3270,30 +3309,30 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">Segmenti!$K$38</f>
@@ -3322,7 +3361,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">-B8*Input!$B$39</f>
@@ -3351,7 +3390,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">-(B8+B9)*Input!$B$38</f>
@@ -3380,7 +3419,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">B8+B9+B10</f>
@@ -3409,7 +3448,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">Input!$B$33</f>
@@ -3438,7 +3477,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">B11+B12</f>
@@ -3467,7 +3506,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B14" s="15" t="n">
         <f aca="false">B13*(1+Ponte!$B$4)^Input!$B$34</f>
@@ -3496,7 +3535,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B15" s="47" t="n">
         <f aca="false">(B14-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
@@ -3525,7 +3564,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B16" s="48" t="n">
         <f aca="false">Input!$B$40/B15</f>
@@ -3554,7 +3593,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -3583,7 +3622,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3602,24 +3641,24 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B4" s="39" t="n">
         <f aca="false">Input!$B$52/(Input!$B$51+Input!$B$52)</f>
         <v>0.2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B5" s="15" t="n">
         <f aca="false">Sinergie!$B$47+Sinergie!$B$48</f>
@@ -3628,7 +3667,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">Sinergie!$B$49</f>
@@ -3637,7 +3676,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B7" s="39" t="n">
         <f aca="false">B6/(B5+B6)</f>
@@ -3646,7 +3685,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">Sinergie!$B$14</f>
@@ -3655,7 +3694,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">(1-B4)*B8</f>
@@ -3664,7 +3703,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">B9-B5</f>
@@ -3673,7 +3712,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">B4*B8</f>
@@ -3682,7 +3721,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">B11-B6</f>
@@ -3691,7 +3730,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">B10+B12</f>
@@ -3700,7 +3739,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">B10/B13</f>
@@ -3709,19 +3748,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">1-B5/B8</f>
         <v>0.263129616011362</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -3751,7 +3790,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3770,25 +3809,25 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B6" s="49" t="n">
         <v>32.68</v>
@@ -3796,7 +3835,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B7" s="49" t="n">
         <v>35.49</v>
@@ -3804,7 +3843,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>15.42</v>
@@ -3812,7 +3851,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B9" s="49" t="n">
         <v>22.79</v>
@@ -3820,7 +3859,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>25.93</v>
@@ -3828,7 +3867,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B11" s="49" t="n">
         <v>19.2</v>
@@ -3836,7 +3875,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B12" s="49" t="n">
         <v>13.51</v>
@@ -3844,7 +3883,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B13" s="49" t="n">
         <v>18.8</v>
@@ -3852,7 +3891,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B14" s="49" t="n">
         <v>20.92</v>
@@ -3860,7 +3899,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B15" s="49" t="n">
         <v>8.55</v>
@@ -3868,7 +3907,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B16" s="49" t="n">
         <v>12.66</v>
@@ -3876,7 +3915,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B17" s="49" t="n">
         <v>19.67</v>
@@ -3884,7 +3923,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B18" s="49" t="n">
         <v>35.01</v>
@@ -3892,7 +3931,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B19" s="49" t="n">
         <v>37.71</v>
@@ -3900,7 +3939,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B20" s="49" t="n">
         <v>32.21</v>
@@ -3908,7 +3947,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B21" s="49" t="n">
         <v>16.03</v>
@@ -3916,7 +3955,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B22" s="49" t="n">
         <v>14.41</v>
@@ -3924,7 +3963,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B23" s="49" t="n">
         <v>16.63</v>
@@ -3932,7 +3971,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B24" s="49" t="n">
         <v>18.16</v>
@@ -3940,12 +3979,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -3957,7 +3996,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>2960</v>
@@ -3965,7 +4004,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>775.68</v>
@@ -3983,26 +4022,26 @@
         <v>34</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>34.3</v>
@@ -4020,12 +4059,12 @@
         <v>1212.8306992886</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>45.6</v>
@@ -4043,12 +4082,12 @@
         <v>1201.89392506626</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E34" s="15" t="n">
         <f aca="false">SUM(E32:E33)</f>
@@ -4057,7 +4096,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E35" s="21" t="n">
         <f aca="false">LN(B29/E34)</f>
@@ -4066,12 +4105,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4083,7 +4122,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>281.19</v>
@@ -4091,7 +4130,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>93.5</v>
@@ -4109,26 +4148,26 @@
         <v>34</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>4.741</v>
@@ -4146,12 +4185,12 @@
         <v>175.162024097065</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>2.596</v>
@@ -4169,12 +4208,12 @@
         <v>88.2415853273138</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3.227</v>
@@ -4192,12 +4231,12 @@
         <v>55.6112989277652</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E45" s="15" t="n">
         <f aca="false">SUM(E42:E44)</f>
@@ -4206,7 +4245,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">LN(B39/E45)</f>
@@ -4215,12 +4254,12 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -4232,7 +4271,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B50" s="12" t="n">
         <v>227.42</v>
@@ -4240,7 +4279,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>98.86</v>
@@ -4258,26 +4297,26 @@
         <v>34</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B53" s="11" t="n">
         <v>9.995</v>
@@ -4295,12 +4334,12 @@
         <v>196.731661742123</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B54" s="11" t="n">
         <v>4.674</v>
@@ -4318,12 +4357,12 @@
         <v>61.9520991517077</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B55" s="11" t="n">
         <v>2.882</v>
@@ -4341,12 +4380,12 @@
         <v>25.7984553455123</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E56" s="15" t="n">
         <f aca="false">SUM(E53:E55)</f>
@@ -4355,7 +4394,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E57" s="21" t="n">
         <f aca="false">LN(B50/E56)</f>
@@ -4364,12 +4403,12 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -4381,16 +4420,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -4401,7 +4440,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B62" s="25" t="n">
         <v>0.576</v>
@@ -4411,15 +4450,15 @@
         <v>-0.858021823750179</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B63" s="25" t="n">
         <v>0.494</v>
@@ -4429,15 +4468,15 @@
         <v>-0.681218609694672</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B64" s="25" t="n">
         <v>0.358</v>
@@ -4447,15 +4486,15 @@
         <v>-0.443166975292176</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -4467,7 +4506,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C67" s="50" t="n">
         <f aca="false">Sinergie!$B$19</f>
@@ -4476,7 +4515,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B68" s="15" t="n">
         <f aca="false">Input!$B$42/(1-Input!$B$38)</f>
@@ -4485,7 +4524,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C69" s="21" t="n">
         <f aca="false">LN(B68/Sinergie!$B$5)</f>
@@ -4494,7 +4533,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C70" s="16" t="n">
         <f aca="false">(((Sinergie!$B$5*EXP(Conglomerati!$E$35))*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
@@ -4503,7 +4542,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C71" s="15" t="n">
         <f aca="false">B68-Sinergie!$B$5</f>
@@ -4512,7 +4551,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="C72" s="18" t="n">
         <f aca="false">C71/Sinergie!$B$18</f>
@@ -4521,73 +4560,73 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="17" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>551</v>
-      </c>
       <c r="H79" s="3" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -4606,7 +4645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -4616,7 +4655,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4635,26 +4674,26 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="B5" s="37" t="n">
         <f aca="false">Segmenti!$K$38</f>
@@ -4670,7 +4709,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="B6" s="37" t="n">
         <f aca="false">Segmenti!$D$38</f>
@@ -4686,7 +4725,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="B7" s="37" t="n">
         <f aca="false">Segmenti!$K$14</f>
@@ -4702,7 +4741,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="B8" s="37" t="n">
         <f aca="false">Segmenti!$K$25</f>
@@ -4718,7 +4757,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">Segmenti!$K$36</f>
@@ -4734,7 +4773,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="B10" s="44" t="n">
         <f aca="false">Ponte!$B$15</f>
@@ -4750,7 +4789,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="B11" s="44" t="n">
         <f aca="false">Ponte!$F$15</f>
@@ -4766,7 +4805,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="B12" s="37" t="n">
         <f aca="false">Sinergie!$B$5</f>
@@ -4782,7 +4821,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B13" s="37" t="n">
         <f aca="false">Sinergie!$B$14</f>
@@ -4798,7 +4837,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B14" s="44" t="n">
         <f aca="false">Ponte!$D$15</f>
@@ -4814,7 +4853,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B15" s="44" t="n">
         <f aca="false">Ponte!$E$15</f>
@@ -4830,7 +4869,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B16" s="37" t="n">
         <f aca="false">Sinergie!$B$16</f>
@@ -4846,7 +4885,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">Sinergie!$B$19</f>
@@ -4862,7 +4901,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">Conglomerati!$C$69</f>
@@ -4878,7 +4917,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="B19" s="44" t="n">
         <f aca="false">Prezzo!$D$23</f>
@@ -4894,7 +4933,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="B20" s="44" t="n">
         <f aca="false">Prezzo!$E$23</f>
@@ -4910,7 +4949,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B21" s="44" t="n">
         <f aca="false">Prezzo!$E$32</f>
@@ -4926,7 +4965,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="B22" s="37" t="n">
         <f aca="false">Prezzo!$B$35</f>
@@ -4942,7 +4981,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">Prezzo!$B$43</f>
@@ -4958,10 +4997,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="B24" s="39" t="n">
-        <f aca="false">Prezzo!$B$51</f>
+        <f aca="false">Prezzo!$B$58</f>
         <v>0.358333781993013</v>
       </c>
       <c r="C24" s="54" t="n">
@@ -4974,33 +5013,65 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="B25" s="15" t="n">
-        <f aca="false">Prezzo!$B$72</f>
-        <v>227.5</v>
-      </c>
-      <c r="C25" s="55" t="n">
-        <v>227.5</v>
+        <v>604</v>
+      </c>
+      <c r="B25" s="44" t="n">
+        <f aca="false">Prezzo!$D$54</f>
+        <v>152.196835787195</v>
+      </c>
+      <c r="C25" s="53" t="n">
+        <v>152.162857063191</v>
       </c>
       <c r="D25" s="52" t="n">
         <f aca="false">B25-C25</f>
-        <v>0</v>
+        <v>0.03397872400393</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="B26" s="15" t="n">
-        <f aca="false">Prezzo!$B$73</f>
-        <v>173</v>
-      </c>
-      <c r="C26" s="55" t="n">
-        <v>173</v>
+        <v>605</v>
+      </c>
+      <c r="B26" s="44" t="n">
+        <f aca="false">Prezzo!$E$54</f>
+        <v>182.628504661712</v>
+      </c>
+      <c r="C26" s="53" t="n">
+        <v>182.573400308311</v>
       </c>
       <c r="D26" s="52" t="n">
         <f aca="false">B26-C26</f>
+        <v>0.0551043534010773</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <f aca="false">Prezzo!$B$79</f>
+        <v>227.5</v>
+      </c>
+      <c r="C27" s="55" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="D27" s="52" t="n">
+        <f aca="false">B27-C27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B28" s="15" t="n">
+        <f aca="false">Prezzo!$B$80</f>
+        <v>173</v>
+      </c>
+      <c r="C28" s="55" t="n">
+        <v>173</v>
+      </c>
+      <c r="D28" s="52" t="n">
+        <f aca="false">B28-C28</f>
         <v>0</v>
       </c>
     </row>
@@ -5020,7 +5091,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -5558,320 +5629,430 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>138.88536010873</v>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>138.88536010873</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+B51)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>60.056741862029</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+C51)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>60.056741862029</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>394.886676905596</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>394.886676905596</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+B52)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>79.1670012129092</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+C52)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>79.1670012129092</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>710.163377480954</v>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>826.179946084019</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+B53)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>102.70211263605</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+C53)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>111.362641194045</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>1373.19542056026</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1780.85850671527</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+B54)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>152.196835787195</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <f aca="false">(((Sinergie!$B$14-138.88536010873+C54)*(1-Input!$B$38)+Input!$B$33)*(1+Ponte!$B$4)^Input!$B$34-Input!$B$36)/(Input!$B$35/1000+Input!$B$37)</f>
+        <v>182.628504661712</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="9" t="n">
         <f aca="false">Ponte!$E$15</f>
         <v>60.056741862029</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" s="21" t="n">
-        <f aca="false">Prezzo!$B$50/Prezzo!$B$5</f>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="21" t="n">
+        <f aca="false">Prezzo!$B$57/Prezzo!$B$5</f>
         <v>0.358333781993013</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="21" t="n">
-        <f aca="false">Prezzo!$B$50/Prezzo!$B$6</f>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="21" t="n">
+        <f aca="false">Prezzo!$B$57/Prezzo!$B$6</f>
         <v>0.444864754533548</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="9" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="9" t="n">
         <f aca="false">Ponte!$F$15</f>
         <v>89.9520296405152</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" s="22" t="n">
-        <v>235</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="22" t="n">
-        <v>230</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B61" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="22" t="n">
-        <v>190</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>87</v>
+      <c r="B63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B64" s="22" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B65" s="22" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B66" s="22" t="n">
+        <v>230</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B66" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="F66" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="22" t="n">
+        <v>225</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B67" s="22" t="n">
-        <v>200</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B68" s="22" t="n">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B69" s="22" t="n">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B70" s="22" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B71" s="22" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B72" s="23" t="n">
-        <f aca="false">MEDIAN(B57:B64)</f>
-        <v>227.5</v>
+        <v>106</v>
+      </c>
+      <c r="B72" s="22" t="n">
+        <v>230</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B73" s="23" t="n">
-        <f aca="false">MEDIAN(B65:B71)</f>
-        <v>173</v>
+        <v>108</v>
+      </c>
+      <c r="B73" s="22" t="n">
+        <v>225</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" s="24" t="n">
-        <v>0.0486</v>
+        <v>109</v>
+      </c>
+      <c r="B74" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="22" t="n">
+        <v>173</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="25" t="n">
+      <c r="F75" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" s="22" t="n">
+        <v>160</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" s="22" t="n">
+        <v>131</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="23" t="n">
+        <f aca="false">MEDIAN(B64:B71)</f>
+        <v>227.5</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B80" s="23" t="n">
+        <f aca="false">MEDIAN(B72:B78)</f>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="24" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B82" s="25" t="n">
         <v>0.19</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>108</v>
+      <c r="F82" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5902,7 +6083,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5921,12 +6102,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5944,103 +6125,103 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>0.053</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>0.042</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>0.001271</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>0.0603</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>0.21</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B10" s="25" t="n">
         <v>0.05</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B11" s="25" t="n">
         <v>0.15</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>0.0415</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6058,79 +6239,79 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B14" s="26" t="n">
         <v>1.25</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>0.822</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B17" s="27" t="n">
         <v>0.469</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B18" s="26" t="n">
         <v>1.6</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>1.227</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -6148,159 +6329,159 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>-1.204</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2.376401179941</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>3.64368</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2.88135974153673</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>-3.28240460526316</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>25.1422390785223</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B31" s="25" t="n">
         <v>0.3</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -6318,143 +6499,143 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>52.03</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>0.27</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B35" s="28" t="n">
         <v>12421.877666</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B36" s="26" t="n">
         <v>-3.81085946261403</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B37" s="26" t="n">
         <v>0.782238426417993</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B38" s="25" t="n">
         <v>0.035</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B39" s="25" t="n">
         <v>0.05</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B40" s="29" t="n">
         <v>167.6</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B41" s="29" t="n">
         <v>135</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>2157.75640878065</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -6472,135 +6653,135 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0.8</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0.05</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>0.03</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>100</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>250</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>2150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -6618,54 +6799,54 @@
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="31" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>34</v>
       </c>
       <c r="C56" s="31" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G56" s="31" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="I56" s="31" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="J56" s="31" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="K56" s="31" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L56" s="31" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="M56" s="31" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2026</v>
@@ -6691,13 +6872,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D58" s="22" t="n">
         <v>2027</v>
@@ -6723,13 +6904,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D59" s="22" t="n">
         <v>2028</v>
@@ -6755,13 +6936,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>2029</v>
@@ -6787,13 +6968,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2030</v>
@@ -6802,18 +6983,18 @@
         <v>0.1</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D62" s="22" t="n">
         <v>2026</v>
@@ -6839,13 +7020,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D63" s="22" t="n">
         <v>2028</v>
@@ -6871,13 +7052,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D64" s="22" t="n">
         <v>2029</v>
@@ -6903,13 +7084,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D65" s="22" t="n">
         <v>2027</v>
@@ -6935,13 +7116,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D66" s="22" t="n">
         <v>2028</v>
@@ -6967,13 +7148,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D67" s="22" t="n">
         <v>2026</v>
@@ -7002,13 +7183,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D68" s="22" t="n">
         <v>2027</v>
@@ -7034,13 +7215,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D69" s="22" t="n">
         <v>2028</v>
@@ -7066,13 +7247,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D70" s="22" t="n">
         <v>2029</v>
@@ -7081,18 +7262,18 @@
         <v>0.13</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D71" s="22" t="n">
         <v>2032</v>
@@ -7118,13 +7299,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D72" s="22" t="n">
         <v>2028</v>
@@ -7150,7 +7331,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -7179,7 +7360,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7198,12 +7379,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>40</v>
@@ -7215,12 +7396,12 @@
         <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B5" s="32" t="n">
         <f aca="false">Input!$B$14</f>
@@ -7241,7 +7422,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B6" s="32" t="n">
         <f aca="false">Input!$B$15</f>
@@ -7262,7 +7443,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B7" s="33" t="n">
         <f aca="false">Input!$B$10</f>
@@ -7283,7 +7464,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">Input!$B$11</f>
@@ -7304,7 +7485,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">Input!$B$5+B5*(1+B7/(1-B7))*Input!$B$6+Input!$B$7</f>
@@ -7325,7 +7506,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B10" s="34" t="n">
         <f aca="false">B7*Input!$B$8*(1-Input!$B$9)+(1-B7)*B9</f>
@@ -7346,7 +7527,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">Input!$B$5+B6*(1+B7/(1-B7))*Input!$B$6+Input!$B$7</f>
@@ -7367,7 +7548,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">B7*Input!$B$8*(1-Input!$B$9)+(1-B7)*B11</f>
@@ -7388,7 +7569,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">Input!$B$5+B6*(1+B8/(1-B8))*Input!$B$6+Input!$B$7</f>
@@ -7409,7 +7590,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B14" s="34" t="n">
         <f aca="false">B8*Input!$B$8*(1-Input!$B$9)+(1-B8)*B13</f>
@@ -7430,7 +7611,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B15" s="35" t="n">
         <f aca="false">MAX(Probabilita!$D$6,Probabilita!$D$7)</f>
@@ -7451,10 +7632,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D18" s="36" t="n">
         <v>2027</v>
@@ -7489,7 +7670,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>2026</v>
@@ -7527,7 +7708,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>0.5</v>
@@ -7575,7 +7756,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C22" s="34" t="n">
         <f aca="false">IF(C$19&lt;=$B$15,$B$10,$B$12)</f>
@@ -7624,7 +7805,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C23" s="38" t="n">
         <f aca="false">1/(1+C22)^C$20</f>
@@ -7673,7 +7854,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C25" s="34" t="n">
         <f aca="false">$B$12</f>
@@ -7722,7 +7903,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C26" s="38" t="n">
         <f aca="false">1/(1+C25)^C$20</f>
@@ -7771,7 +7952,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C28" s="34" t="n">
         <f aca="false">IF(C$19&lt;=$C$15,$C$10,$C$12)</f>
@@ -7820,7 +8001,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C29" s="38" t="n">
         <f aca="false">1/(1+C28)^C$20</f>
@@ -7869,7 +8050,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">$C$12</f>
@@ -7918,7 +8099,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C32" s="38" t="n">
         <f aca="false">1/(1+C31)^C$20</f>
@@ -7967,7 +8148,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C34" s="34" t="n">
         <f aca="false">IF(C$19&lt;=$D$15,$D$10,$D$12)</f>
@@ -8016,7 +8197,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C35" s="38" t="n">
         <f aca="false">1/(1+C34)^C$20</f>
@@ -8065,7 +8246,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C37" s="34" t="n">
         <f aca="false">$D$12</f>
@@ -8114,7 +8295,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C38" s="38" t="n">
         <f aca="false">1/(1+C37)^C$20</f>
@@ -8163,7 +8344,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C40" s="34" t="n">
         <f aca="false">IF(C$19&lt;=$E$15,$E$10,$E$12)</f>
@@ -8212,7 +8393,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C41" s="38" t="n">
         <f aca="false">1/(1+C40)^C$20</f>
@@ -8261,7 +8442,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C43" s="34" t="n">
         <f aca="false">$E$12</f>
@@ -8310,7 +8491,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C44" s="38" t="n">
         <f aca="false">1/(1+C43)^C$20</f>
@@ -8391,7 +8572,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8410,73 +8591,73 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H3" s="17" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D5" s="22" t="n">
         <v>2027</v>
@@ -8524,13 +8705,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D6" s="22" t="n">
         <v>2028</v>
@@ -8578,13 +8759,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D7" s="22" t="n">
         <v>2028</v>
@@ -8633,13 +8814,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>2029</v>
@@ -8688,13 +8869,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D9" s="22" t="n">
         <v>2030</v>
@@ -8742,13 +8923,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>2028</v>
@@ -8796,13 +8977,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>2027</v>
@@ -8851,13 +9032,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>2030</v>
@@ -8906,13 +9087,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>2028</v>
@@ -8961,13 +9142,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>2027</v>
@@ -9016,13 +9197,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>2028</v>
@@ -9071,13 +9252,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>2029</v>
@@ -9126,13 +9307,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D17" s="22" t="n">
         <v>2032</v>
@@ -9180,7 +9361,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9213,7 +9394,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9232,12 +9413,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C4" s="36" t="n">
         <v>2026</v>
@@ -9278,7 +9459,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -9299,7 +9480,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Input!$E$57</f>
@@ -9350,7 +9531,7 @@
         <v>12.498</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q7" s="37" t="n">
         <f aca="false">N7*Input!$I$57*(1-Input!$B$9)</f>
@@ -9359,7 +9540,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D8" s="39" t="n">
         <f aca="false">IF(D$4&lt;=2027,Input!$H$57,IF(D$4&gt;=(2027+4),Input!$I$57,Input!$H$57+(Input!$I$57-Input!$H$57)*(D$4-2027)/(((2027+4))-(2027))))</f>
@@ -9402,7 +9583,7 @@
         <v>0.2</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q8" s="37" t="n">
         <f aca="false">Q7*(1-Input!$B$12/Input!$K$57)</f>
@@ -9411,7 +9592,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">D7*D8</f>
@@ -9454,7 +9635,7 @@
         <v>2.4</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q9" s="15" t="n">
         <f aca="false">Q8/(Tassi!$B$14-Input!$B$12)</f>
@@ -9463,7 +9644,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D10" s="37" t="n">
         <f aca="false">(E7-D7)/Input!$J$57</f>
@@ -9506,7 +9687,7 @@
         <v>0.355714285714287</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q10" s="15" t="n">
         <f aca="false">SUMPRODUCT($D11:$M11,Tassi!$D$23:$M$23)+Q9*Tassi!$M$23</f>
@@ -9515,7 +9696,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D9*(1-Input!$B$9)-D10</f>
@@ -9558,7 +9739,7 @@
         <v>1.54028571428571</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q11" s="15" t="n">
         <f aca="false">SUMPRODUCT($D11:$M11,Tassi!$D$26:$M$26)+Q9*Tassi!$M$26</f>
@@ -9567,7 +9748,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -9588,7 +9769,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$58,0,IF(C$4&lt;=Input!$D$58,Input!$E$58,IF(C$4&gt;=2036,Input!$F$58,Input!$E$58+(Input!$F$58-Input!$E$58)*(C$4-Input!$D$58)/((2036)-(Input!$D$58)))))</f>
@@ -9639,7 +9820,7 @@
         <v>6.249</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q16" s="37" t="n">
         <f aca="false">N16*Input!$I$58*(1-Input!$B$9)</f>
@@ -9648,7 +9829,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D17" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$58,Input!$H$58,IF(D$4&gt;=(Input!$D$58+4),Input!$I$58,Input!$H$58+(Input!$I$58-Input!$H$58)*(D$4-Input!$D$58)/(((Input!$D$58+4))-(Input!$D$58))))</f>
@@ -9691,7 +9872,7 @@
         <v>0.2</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q17" s="37" t="n">
         <f aca="false">Q16*(1-Input!$B$12/Input!$K$58)</f>
@@ -9700,7 +9881,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D18" s="37" t="n">
         <f aca="false">D16*D17</f>
@@ -9743,7 +9924,7 @@
         <v>1.2</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q18" s="15" t="n">
         <f aca="false">Q17/(Tassi!$B$14-Input!$B$12)</f>
@@ -9752,7 +9933,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">(E16-D16)/Input!$J$58</f>
@@ -9795,7 +9976,7 @@
         <v>0.249000000000001</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q19" s="15" t="n">
         <f aca="false">SUMPRODUCT($D20:$M20,Tassi!$D$23:$M$23)+Q18*Tassi!$M$23</f>
@@ -9804,7 +9985,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">D18*(1-Input!$B$9)-D19</f>
@@ -9847,7 +10028,7 @@
         <v>0.699</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q20" s="15" t="n">
         <f aca="false">SUMPRODUCT($D20:$M20,Tassi!$D$26:$M$26)+Q18*Tassi!$M$26</f>
@@ -9856,7 +10037,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -9877,7 +10058,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C25" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$59,0,IF(C$4&lt;=Input!$D$59,Input!$E$59,IF(C$4&gt;=2036,Input!$F$59,Input!$E$59+(Input!$F$59-Input!$E$59)*(C$4-Input!$D$59)/((2036)-(Input!$D$59)))))</f>
@@ -9928,7 +10109,7 @@
         <v>8.332</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q25" s="37" t="n">
         <f aca="false">N25*Input!$I$59*(1-Input!$B$9)</f>
@@ -9937,7 +10118,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D26" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$59,Input!$H$59,IF(D$4&gt;=(Input!$D$59+4),Input!$I$59,Input!$H$59+(Input!$I$59-Input!$H$59)*(D$4-Input!$D$59)/(((Input!$D$59+4))-(Input!$D$59))))</f>
@@ -9980,7 +10161,7 @@
         <v>0.25</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q26" s="37" t="n">
         <f aca="false">Q25*(1-Input!$B$12/Input!$K$59)</f>
@@ -9989,7 +10170,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">D25*D26</f>
@@ -10032,7 +10213,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q27" s="15" t="n">
         <f aca="false">Q26/(Tassi!$B$14-Input!$B$12)</f>
@@ -10041,7 +10222,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D28" s="37" t="n">
         <f aca="false">(E25-D25)/Input!$J$59</f>
@@ -10084,7 +10265,7 @@
         <v>0.332000000000001</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q28" s="15" t="n">
         <f aca="false">SUMPRODUCT($D29:$M29,Tassi!$D$23:$M$23)+Q27*Tassi!$M$23</f>
@@ -10093,7 +10274,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D29" s="37" t="n">
         <f aca="false">D27*(1-Input!$B$9)-D28</f>
@@ -10136,7 +10317,7 @@
         <v>1.248</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q29" s="15" t="n">
         <f aca="false">SUMPRODUCT($D29:$M29,Tassi!$D$26:$M$26)+Q27*Tassi!$M$26</f>
@@ -10145,7 +10326,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -10166,7 +10347,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$60,0,IF(C$4&lt;=Input!$D$60,Input!$E$60,IF(C$4&gt;=2036,Input!$F$60,Input!$E$60+(Input!$F$60-Input!$E$60)*(C$4-Input!$D$60)/((2036)-(Input!$D$60)))))</f>
@@ -10217,7 +10398,7 @@
         <v>4.166</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q34" s="37" t="n">
         <f aca="false">N34*Input!$I$60*(1-Input!$B$9)</f>
@@ -10226,7 +10407,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D35" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$60,Input!$H$60,IF(D$4&gt;=(Input!$D$60+4),Input!$I$60,Input!$H$60+(Input!$I$60-Input!$H$60)*(D$4-Input!$D$60)/(((Input!$D$60+4))-(Input!$D$60))))</f>
@@ -10269,7 +10450,7 @@
         <v>0.15</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q35" s="37" t="n">
         <f aca="false">Q34*(1-Input!$B$12/Input!$K$60)</f>
@@ -10278,7 +10459,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D36" s="37" t="n">
         <f aca="false">D34*D35</f>
@@ -10321,7 +10502,7 @@
         <v>0.6</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q36" s="15" t="n">
         <f aca="false">Q35/(Tassi!$B$14-Input!$B$12)</f>
@@ -10330,7 +10511,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D37" s="37" t="n">
         <f aca="false">(E34-D34)/Input!$J$60</f>
@@ -10373,7 +10554,7 @@
         <v>0.0830000000000002</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q37" s="15" t="n">
         <f aca="false">SUMPRODUCT($D38:$M38,Tassi!$D$23:$M$23)+Q36*Tassi!$M$23</f>
@@ -10382,7 +10563,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D38" s="37" t="n">
         <f aca="false">D36*(1-Input!$B$9)-D37</f>
@@ -10425,7 +10606,7 @@
         <v>0.391</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q38" s="15" t="n">
         <f aca="false">SUMPRODUCT($D38:$M38,Tassi!$D$26:$M$26)+Q36*Tassi!$M$26</f>
@@ -10434,7 +10615,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -10455,10 +10636,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C43" s="15" t="n">
         <f aca="false">C7+C16+C25</f>
@@ -10509,7 +10690,7 @@
         <v>27.079</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q43" s="37" t="n">
         <f aca="false">Input!$L$61*M43*(1+Input!$B$12)*(1-Input!$B$9)</f>
@@ -10518,7 +10699,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D44" s="39" t="n">
         <f aca="false">IF(D$4&lt;=(Input!$D$61-1),0,IF(D$4&gt;=(Input!$D$61+2),Input!$L$61,0+(Input!$L$61-0)*(D$4-(Input!$D$61-1))/(((Input!$D$61+2))-((Input!$D$61-1)))))</f>
@@ -10561,7 +10742,7 @@
         <v>0.1</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q44" s="37" t="n">
         <f aca="false">Q43</f>
@@ -10570,7 +10751,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D45" s="37" t="n">
         <f aca="false">D43*D44</f>
@@ -10613,7 +10794,7 @@
         <v>2.6</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q45" s="15" t="n">
         <f aca="false">Q44/(Tassi!$B$14-Input!$B$12)</f>
@@ -10622,7 +10803,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D46" s="37" t="n">
         <v>0</v>
@@ -10655,7 +10836,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q46" s="15" t="n">
         <f aca="false">SUMPRODUCT($D47:$M47,Tassi!$D$23:$M$23)+Q45*Tassi!$M$23</f>
@@ -10664,7 +10845,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D47" s="37" t="n">
         <f aca="false">D45*(1-Input!$B$9)-D46</f>
@@ -10707,7 +10888,7 @@
         <v>2.054</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q47" s="15" t="n">
         <f aca="false">SUMPRODUCT($D47:$M47,Tassi!$D$26:$M$26)+Q45*Tassi!$M$26</f>
@@ -10716,7 +10897,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -10737,7 +10918,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C52" s="10" t="n">
         <f aca="false">Input!$E$62</f>
@@ -10788,7 +10969,7 @@
         <v>83.3200000000001</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q52" s="37" t="n">
         <f aca="false">N52*Input!$I$62*(1-Input!$B$9)</f>
@@ -10797,7 +10978,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D53" s="39" t="n">
         <f aca="false">IF(D$4&lt;=2027,Input!$H$62,IF(D$4&gt;=(2027+4),Input!$I$62,Input!$H$62+(Input!$I$62-Input!$H$62)*(D$4-2027)/(((2027+4))-(2027))))</f>
@@ -10840,7 +11021,7 @@
         <v>0.45</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q53" s="37" t="n">
         <f aca="false">Q52*(1-Input!$B$12/Input!$K$62)</f>
@@ -10849,7 +11030,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D54" s="37" t="n">
         <f aca="false">D52*D53</f>
@@ -10892,7 +11073,7 @@
         <v>36</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q54" s="15" t="n">
         <f aca="false">Q53/(Tassi!$C$14-Input!$B$12)</f>
@@ -10901,7 +11082,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D55" s="37" t="n">
         <f aca="false">(E52-D52)/Input!$J$62</f>
@@ -10944,7 +11125,7 @@
         <v>1.18571428571429</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q55" s="15" t="n">
         <f aca="false">SUMPRODUCT($D56:$M56,Tassi!$D$29:$M$29)+Q54*Tassi!$M$29</f>
@@ -10953,7 +11134,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D56" s="37" t="n">
         <f aca="false">D54*(1-Input!$B$9)-D55</f>
@@ -10996,7 +11177,7 @@
         <v>27.2542857142857</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q56" s="15" t="n">
         <f aca="false">SUMPRODUCT($D56:$M56,Tassi!$D$32:$M$32)+Q54*Tassi!$M$32</f>
@@ -11005,7 +11186,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -11026,7 +11207,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C61" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$63,0,IF(C$4&lt;=Input!$D$63,Input!$E$63,IF(C$4&gt;=2036,Input!$F$63,Input!$E$63+(Input!$F$63-Input!$E$63)*(C$4-Input!$D$63)/((2036)-(Input!$D$63)))))</f>
@@ -11077,7 +11258,7 @@
         <v>31.245</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q61" s="37" t="n">
         <f aca="false">N61*Input!$I$63*(1-Input!$B$9)</f>
@@ -11086,7 +11267,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D62" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$63,Input!$H$63,IF(D$4&gt;=(Input!$D$63+4),Input!$I$63,Input!$H$63+(Input!$I$63-Input!$H$63)*(D$4-Input!$D$63)/(((Input!$D$63+4))-(Input!$D$63))))</f>
@@ -11129,7 +11310,7 @@
         <v>0.45</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q62" s="37" t="n">
         <f aca="false">Q61*(1-Input!$B$12/Input!$K$63)</f>
@@ -11138,7 +11319,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D63" s="37" t="n">
         <f aca="false">D61*D62</f>
@@ -11181,7 +11362,7 @@
         <v>13.5</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q63" s="15" t="n">
         <f aca="false">Q62/(Tassi!$C$14-Input!$B$12)</f>
@@ -11190,7 +11371,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D64" s="37" t="n">
         <f aca="false">(E61-D61)/Input!$J$63</f>
@@ -11233,7 +11414,7 @@
         <v>0.622500000000002</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q64" s="15" t="n">
         <f aca="false">SUMPRODUCT($D65:$M65,Tassi!$D$29:$M$29)+Q63*Tassi!$M$29</f>
@@ -11242,7 +11423,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D65" s="37" t="n">
         <f aca="false">D63*(1-Input!$B$9)-D64</f>
@@ -11285,7 +11466,7 @@
         <v>10.0425</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q65" s="15" t="n">
         <f aca="false">SUMPRODUCT($D65:$M65,Tassi!$D$32:$M$32)+Q63*Tassi!$M$32</f>
@@ -11294,7 +11475,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -11315,7 +11496,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C70" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$64,0,IF(C$4&lt;=Input!$D$64,Input!$E$64,IF(C$4&gt;=2036,Input!$F$64,Input!$E$64+(Input!$F$64-Input!$E$64)*(C$4-Input!$D$64)/((2036)-(Input!$D$64)))))</f>
@@ -11366,7 +11547,7 @@
         <v>15.6225</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q70" s="37" t="n">
         <f aca="false">N70*Input!$I$64*(1-Input!$B$9)</f>
@@ -11375,7 +11556,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D71" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$64,Input!$H$64,IF(D$4&gt;=(Input!$D$64+4),Input!$I$64,Input!$H$64+(Input!$I$64-Input!$H$64)*(D$4-Input!$D$64)/(((Input!$D$64+4))-(Input!$D$64))))</f>
@@ -11418,7 +11599,7 @@
         <v>0.45</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q71" s="37" t="n">
         <f aca="false">Q70*(1-Input!$B$12/Input!$K$64)</f>
@@ -11427,7 +11608,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D72" s="37" t="n">
         <f aca="false">D70*D71</f>
@@ -11470,7 +11651,7 @@
         <v>6.75</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q72" s="15" t="n">
         <f aca="false">Q71/(Tassi!$C$14-Input!$B$12)</f>
@@ -11479,7 +11660,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D73" s="37" t="n">
         <f aca="false">(E70-D70)/Input!$J$64</f>
@@ -11522,7 +11703,7 @@
         <v>0.222321428571429</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q73" s="15" t="n">
         <f aca="false">SUMPRODUCT($D74:$M74,Tassi!$D$29:$M$29)+Q72*Tassi!$M$29</f>
@@ -11531,7 +11712,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D74" s="37" t="n">
         <f aca="false">D72*(1-Input!$B$9)-D73</f>
@@ -11574,7 +11755,7 @@
         <v>5.11017857142857</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q74" s="15" t="n">
         <f aca="false">SUMPRODUCT($D74:$M74,Tassi!$D$32:$M$32)+Q72*Tassi!$M$32</f>
@@ -11583,7 +11764,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -11604,7 +11785,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C79" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$65,0,IF(C$4&lt;=Input!$D$65,Input!$E$65,IF(C$4&gt;=2036,Input!$F$65,Input!$E$65+(Input!$F$65-Input!$E$65)*(C$4-Input!$D$65)/((2036)-(Input!$D$65)))))</f>
@@ -11655,7 +11836,7 @@
         <v>26.0375</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q79" s="37" t="n">
         <f aca="false">N79*Input!$I$65*(1-Input!$B$9)</f>
@@ -11664,7 +11845,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D80" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$65,Input!$H$65,IF(D$4&gt;=(Input!$D$65+4),Input!$I$65,Input!$H$65+(Input!$I$65-Input!$H$65)*(D$4-Input!$D$65)/(((Input!$D$65+4))-(Input!$D$65))))</f>
@@ -11707,7 +11888,7 @@
         <v>0.35</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q80" s="37" t="n">
         <f aca="false">Q79*(1-Input!$B$12/Input!$K$65)</f>
@@ -11716,7 +11897,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D81" s="37" t="n">
         <f aca="false">D79*D80</f>
@@ -11759,7 +11940,7 @@
         <v>8.75</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q81" s="15" t="n">
         <f aca="false">Q80/(Tassi!$C$14-Input!$B$12)</f>
@@ -11768,7 +11949,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D82" s="37" t="n">
         <f aca="false">(E79-D79)/Input!$J$65</f>
@@ -11811,7 +11992,7 @@
         <v>0.691666666666668</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q82" s="15" t="n">
         <f aca="false">SUMPRODUCT($D83:$M83,Tassi!$D$29:$M$29)+Q81*Tassi!$M$29</f>
@@ -11820,7 +12001,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D83" s="37" t="n">
         <f aca="false">D81*(1-Input!$B$9)-D82</f>
@@ -11863,7 +12044,7 @@
         <v>6.22083333333333</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q83" s="15" t="n">
         <f aca="false">SUMPRODUCT($D83:$M83,Tassi!$D$32:$M$32)+Q81*Tassi!$M$32</f>
@@ -11872,7 +12053,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -11893,7 +12074,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C88" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$66,0,IF(C$4&lt;=Input!$D$66,Input!$E$66,IF(C$4&gt;=2036,Input!$F$66,Input!$E$66+(Input!$F$66-Input!$E$66)*(C$4-Input!$D$66)/((2036)-(Input!$D$66)))))</f>
@@ -11944,7 +12125,7 @@
         <v>10.415</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q88" s="37" t="n">
         <f aca="false">N88*Input!$I$66*(1-Input!$B$9)</f>
@@ -11953,7 +12134,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D89" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$66,Input!$H$66,IF(D$4&gt;=(Input!$D$66+4),Input!$I$66,Input!$H$66+(Input!$I$66-Input!$H$66)*(D$4-Input!$D$66)/(((Input!$D$66+4))-(Input!$D$66))))</f>
@@ -11996,7 +12177,7 @@
         <v>0.4</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q89" s="37" t="n">
         <f aca="false">Q88*(1-Input!$B$12/Input!$K$66)</f>
@@ -12005,7 +12186,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D90" s="37" t="n">
         <f aca="false">D88*D89</f>
@@ -12048,7 +12229,7 @@
         <v>4</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q90" s="15" t="n">
         <f aca="false">Q89/(Tassi!$C$14-Input!$B$12)</f>
@@ -12057,7 +12238,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D91" s="37" t="n">
         <f aca="false">(E88-D88)/Input!$J$66</f>
@@ -12100,7 +12281,7 @@
         <v>0.148214285714286</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q91" s="15" t="n">
         <f aca="false">SUMPRODUCT($D92:$M92,Tassi!$D$29:$M$29)+Q90*Tassi!$M$29</f>
@@ -12109,7 +12290,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D92" s="37" t="n">
         <f aca="false">D90*(1-Input!$B$9)-D91</f>
@@ -12152,7 +12333,7 @@
         <v>3.01178571428571</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q92" s="15" t="n">
         <f aca="false">SUMPRODUCT($D92:$M92,Tassi!$D$32:$M$32)+Q90*Tassi!$M$32</f>
@@ -12161,7 +12342,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -12182,7 +12363,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C97" s="10" t="n">
         <f aca="false">Input!$E$67</f>
@@ -12233,7 +12414,7 @@
         <v>62.49</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q97" s="37" t="n">
         <f aca="false">N97*Input!$I$67*(1-Input!$B$9)</f>
@@ -12242,7 +12423,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D98" s="39" t="n">
         <f aca="false">IF(D$4&lt;=2027,Input!$H$67,IF(D$4&gt;=(2027+4),Input!$I$67,Input!$H$67+(Input!$I$67-Input!$H$67)*(D$4-2027)/(((2027+4))-(2027))))</f>
@@ -12285,7 +12466,7 @@
         <v>0.05</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q98" s="37" t="n">
         <f aca="false">Q97*(1-Input!$B$12/Input!$K$67)</f>
@@ -12294,7 +12475,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D99" s="37" t="n">
         <f aca="false">D97*D98</f>
@@ -12337,7 +12518,7 @@
         <v>3</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q99" s="15" t="n">
         <f aca="false">Q98/(Tassi!$D$14-Input!$B$12)</f>
@@ -12346,7 +12527,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D100" s="37" t="n">
         <f aca="false">(E97-D97)/Input!$J$67</f>
@@ -12389,7 +12570,7 @@
         <v>4.98</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q100" s="15" t="n">
         <f aca="false">SUMPRODUCT($D101:$M101,Tassi!$D$35:$M$35)+Q99*Tassi!$M$35</f>
@@ -12398,7 +12579,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D101" s="37" t="n">
         <f aca="false">D99*(1-Input!$B$9)-D100</f>
@@ -12441,7 +12622,7 @@
         <v>-2.61000000000001</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q101" s="15" t="n">
         <f aca="false">SUMPRODUCT($D101:$M101,Tassi!$D$38:$M$38)+Q99*Tassi!$M$38</f>
@@ -12450,7 +12631,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P102" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Q102" s="15" t="n">
         <f aca="false">SUMPRODUCT($D101:$M101,Tassi!$D$41:$M$41)+Q98/(Tassi!$E$14-Input!$B$12)*Tassi!$M$41</f>
@@ -12459,7 +12640,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -12480,7 +12661,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C107" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$68,0,IF(C$4&lt;=Input!$D$68,Input!$E$68,IF(C$4&gt;=2036,Input!$F$68,Input!$E$68+(Input!$F$68-Input!$E$68)*(C$4-Input!$D$68)/((2036)-(Input!$D$68)))))</f>
@@ -12531,7 +12712,7 @@
         <v>93.735</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q107" s="37" t="n">
         <f aca="false">N107*Input!$I$68*(1-Input!$B$9)</f>
@@ -12540,7 +12721,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D108" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$68,Input!$H$68,IF(D$4&gt;=(Input!$D$68+4),Input!$I$68,Input!$H$68+(Input!$I$68-Input!$H$68)*(D$4-Input!$D$68)/(((Input!$D$68+4))-(Input!$D$68))))</f>
@@ -12583,7 +12764,7 @@
         <v>0.17</v>
       </c>
       <c r="P108" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q108" s="37" t="n">
         <f aca="false">Q107*(1-Input!$B$12/Input!$K$68)</f>
@@ -12592,7 +12773,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D109" s="37" t="n">
         <f aca="false">D107*D108</f>
@@ -12635,7 +12816,7 @@
         <v>15.3</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q109" s="15" t="n">
         <f aca="false">Q108/(Tassi!$D$14-Input!$B$12)</f>
@@ -12644,7 +12825,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D110" s="37" t="n">
         <f aca="false">(E107-D107)/Input!$J$68</f>
@@ -12687,7 +12868,7 @@
         <v>6.22500000000002</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q110" s="15" t="n">
         <f aca="false">SUMPRODUCT($D111:$M111,Tassi!$D$35:$M$35)+Q109*Tassi!$M$35</f>
@@ -12696,7 +12877,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D111" s="37" t="n">
         <f aca="false">D109*(1-Input!$B$9)-D110</f>
@@ -12739,7 +12920,7 @@
         <v>5.86199999999998</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q111" s="15" t="n">
         <f aca="false">SUMPRODUCT($D111:$M111,Tassi!$D$38:$M$38)+Q109*Tassi!$M$38</f>
@@ -12748,7 +12929,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P112" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Q112" s="15" t="n">
         <f aca="false">SUMPRODUCT($D111:$M111,Tassi!$D$41:$M$41)+Q108/(Tassi!$E$14-Input!$B$12)*Tassi!$M$41</f>
@@ -12757,7 +12938,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -12778,7 +12959,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C117" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$69,0,IF(C$4&lt;=Input!$D$69,Input!$E$69,IF(C$4&gt;=2036,Input!$F$69,Input!$E$69+(Input!$F$69-Input!$E$69)*(C$4-Input!$D$69)/((2036)-(Input!$D$69)))))</f>
@@ -12829,7 +13010,7 @@
         <v>312.45</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q117" s="37" t="n">
         <f aca="false">N117*Input!$I$69*(1-Input!$B$9)</f>
@@ -12838,7 +13019,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D118" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$69,Input!$H$69,IF(D$4&gt;=(Input!$D$69+4),Input!$I$69,Input!$H$69+(Input!$I$69-Input!$H$69)*(D$4-Input!$D$69)/(((Input!$D$69+4))-(Input!$D$69))))</f>
@@ -12881,7 +13062,7 @@
         <v>0.31</v>
       </c>
       <c r="P118" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q118" s="37" t="n">
         <f aca="false">Q117*(1-Input!$B$12/Input!$K$69)</f>
@@ -12890,7 +13071,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D119" s="37" t="n">
         <f aca="false">D117*D118</f>
@@ -12933,7 +13114,7 @@
         <v>93</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="15" t="n">
         <f aca="false">Q118/(Tassi!$D$14-Input!$B$12)</f>
@@ -12942,7 +13123,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D120" s="37" t="n">
         <f aca="false">(E117-D117)/Input!$J$69</f>
@@ -12985,7 +13166,7 @@
         <v>12.45</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="15" t="n">
         <f aca="false">SUMPRODUCT($D121:$M121,Tassi!$D$35:$M$35)+Q119*Tassi!$M$35</f>
@@ -12994,7 +13175,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D121" s="37" t="n">
         <f aca="false">D119*(1-Input!$B$9)-D120</f>
@@ -13037,7 +13218,7 @@
         <v>61.02</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="15" t="n">
         <f aca="false">SUMPRODUCT($D121:$M121,Tassi!$D$38:$M$38)+Q119*Tassi!$M$38</f>
@@ -13046,7 +13227,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P122" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Q122" s="15" t="n">
         <f aca="false">SUMPRODUCT($D121:$M121,Tassi!$D$41:$M$41)+Q118/(Tassi!$E$14-Input!$B$12)*Tassi!$M$41</f>
@@ -13055,7 +13236,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -13076,10 +13257,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C127" s="15" t="n">
         <f aca="false">C107</f>
@@ -13130,7 +13311,7 @@
         <v>93.735</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q127" s="37" t="n">
         <f aca="false">Input!$L$70*M127*(1+Input!$B$12)*(1-Input!$B$9)</f>
@@ -13139,7 +13320,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D128" s="39" t="n">
         <f aca="false">IF(D$4&lt;=(Input!$D$70-1),0,IF(D$4&gt;=(Input!$D$70+2),Input!$L$70,0+(Input!$L$70-0)*(D$4-(Input!$D$70-1))/(((Input!$D$70+2))-((Input!$D$70-1)))))</f>
@@ -13182,7 +13363,7 @@
         <v>0.13</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q128" s="37" t="n">
         <f aca="false">Q127</f>
@@ -13191,7 +13372,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D129" s="37" t="n">
         <f aca="false">D127*D128</f>
@@ -13234,7 +13415,7 @@
         <v>11.7</v>
       </c>
       <c r="P129" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q129" s="15" t="n">
         <f aca="false">Q128/(Tassi!$D$14-Input!$B$12)</f>
@@ -13243,7 +13424,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D130" s="37" t="n">
         <v>0</v>
@@ -13276,7 +13457,7 @@
         <v>0</v>
       </c>
       <c r="P130" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q130" s="15" t="n">
         <f aca="false">SUMPRODUCT($D131:$M131,Tassi!$D$35:$M$35)+Q129*Tassi!$M$35</f>
@@ -13285,7 +13466,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D131" s="37" t="n">
         <f aca="false">D129*(1-Input!$B$9)-D130</f>
@@ -13328,7 +13509,7 @@
         <v>9.243</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q131" s="15" t="n">
         <f aca="false">SUMPRODUCT($D131:$M131,Tassi!$D$38:$M$38)+Q129*Tassi!$M$38</f>
@@ -13337,7 +13518,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P132" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Q132" s="15" t="n">
         <f aca="false">SUMPRODUCT($D131:$M131,Tassi!$D$41:$M$41)+Q128/(Tassi!$E$14-Input!$B$12)*Tassi!$M$41</f>
@@ -13346,7 +13527,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -13367,7 +13548,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C137" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$71,0,IF(C$4&lt;=Input!$D$71,Input!$E$71,IF(C$4&gt;=2036,Input!$F$71,Input!$E$71+(Input!$F$71-Input!$E$71)*(C$4-Input!$D$71)/((2036)-(Input!$D$71)))))</f>
@@ -13418,7 +13599,7 @@
         <v>104.15</v>
       </c>
       <c r="P137" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q137" s="37" t="n">
         <f aca="false">N137*Input!$I$71*(1-Input!$B$9)</f>
@@ -13427,7 +13608,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D138" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$71,Input!$H$71,IF(D$4&gt;=(Input!$D$71+4),Input!$I$71,Input!$H$71+(Input!$I$71-Input!$H$71)*(D$4-Input!$D$71)/(((Input!$D$71+4))-(Input!$D$71))))</f>
@@ -13470,7 +13651,7 @@
         <v>0.35</v>
       </c>
       <c r="P138" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q138" s="37" t="n">
         <f aca="false">Q137*(1-Input!$B$12/Input!$K$71)</f>
@@ -13479,7 +13660,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D139" s="37" t="n">
         <f aca="false">D137*D138</f>
@@ -13522,7 +13703,7 @@
         <v>35</v>
       </c>
       <c r="P139" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q139" s="15" t="n">
         <f aca="false">Q138/(Tassi!$D$14-Input!$B$12)</f>
@@ -13531,7 +13712,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D140" s="37" t="n">
         <f aca="false">(E137-D137)/Input!$J$71</f>
@@ -13574,7 +13755,7 @@
         <v>4.15000000000001</v>
       </c>
       <c r="P140" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q140" s="15" t="n">
         <f aca="false">SUMPRODUCT($D141:$M141,Tassi!$D$35:$M$35)+Q139*Tassi!$M$35</f>
@@ -13583,7 +13764,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D141" s="37" t="n">
         <f aca="false">D139*(1-Input!$B$9)-D140</f>
@@ -13626,7 +13807,7 @@
         <v>23.5</v>
       </c>
       <c r="P141" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q141" s="15" t="n">
         <f aca="false">SUMPRODUCT($D141:$M141,Tassi!$D$38:$M$38)+Q139*Tassi!$M$38</f>
@@ -13635,7 +13816,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P142" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Q142" s="15" t="n">
         <f aca="false">SUMPRODUCT($D141:$M141,Tassi!$D$41:$M$41)+Q138/(Tassi!$E$14-Input!$B$12)*Tassi!$M$41</f>
@@ -13644,7 +13825,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -13665,7 +13846,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C147" s="15" t="n">
         <f aca="false">IF(C$4&lt;Input!$D$72,0,IF(C$4&lt;=Input!$D$72,Input!$E$72,IF(C$4&gt;=2036,Input!$F$72,Input!$E$72+(Input!$F$72-Input!$E$72)*(C$4-Input!$D$72)/((2036)-(Input!$D$72)))))</f>
@@ -13716,7 +13897,7 @@
         <v>12.498</v>
       </c>
       <c r="P147" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Q147" s="37" t="n">
         <f aca="false">N147*Input!$I$72*(1-Input!$B$9)</f>
@@ -13725,7 +13906,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D148" s="39" t="n">
         <f aca="false">IF(D$4&lt;=Input!$D$72,Input!$H$72,IF(D$4&gt;=(Input!$D$72+4),Input!$I$72,Input!$H$72+(Input!$I$72-Input!$H$72)*(D$4-Input!$D$72)/(((Input!$D$72+4))-(Input!$D$72))))</f>
@@ -13768,7 +13949,7 @@
         <v>0.15</v>
       </c>
       <c r="P148" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="Q148" s="37" t="n">
         <f aca="false">Q147*(1-Input!$B$12/Input!$K$72)</f>
@@ -13777,7 +13958,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D149" s="37" t="n">
         <f aca="false">D147*D148</f>
@@ -13820,7 +14001,7 @@
         <v>1.8</v>
       </c>
       <c r="P149" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q149" s="15" t="n">
         <f aca="false">Q148/(Tassi!$B$14-Input!$B$12)</f>
@@ -13829,7 +14010,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="8" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D150" s="37" t="n">
         <f aca="false">(E147-D147)/Input!$J$72</f>
@@ -13872,7 +14053,7 @@
         <v>0.249000000000001</v>
       </c>
       <c r="P150" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Q150" s="15" t="n">
         <f aca="false">SUMPRODUCT($D151:$M151,Tassi!$D$23:$M$23)+Q149*Tassi!$M$23</f>
@@ -13881,7 +14062,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D151" s="37" t="n">
         <f aca="false">D149*(1-Input!$B$9)-D150</f>
@@ -13924,7 +14105,7 @@
         <v>1.173</v>
       </c>
       <c r="P151" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="Q151" s="15" t="n">
         <f aca="false">SUMPRODUCT($D151:$M151,Tassi!$D$26:$M$26)+Q149*Tassi!$M$26</f>
@@ -13959,7 +14140,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13978,49 +14159,49 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14043,10 +14224,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">Blocchi!$Q$10</f>
@@ -14087,10 +14268,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Blocchi!$Q$19</f>
@@ -14135,10 +14316,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">Blocchi!$Q$28</f>
@@ -14183,10 +14364,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">Blocchi!$Q$37</f>
@@ -14231,10 +14412,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">Blocchi!$Q$46</f>
@@ -14279,7 +14460,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="C11" s="15" t="n">
         <f aca="false">(Input!$B$21-Input!$B$22)*Tassi!$C$23</f>
@@ -14292,7 +14473,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">-(Input!$B$27*(1-Input!$B$9)*Tassi!$D$23+Input!$B$28*(1-Input!$B$9)*Tassi!$E$23+Input!$B$29*(1-Input!$B$9)*Tassi!$F$23+Input!$B$30*(1-Input!$B$9)*Tassi!$G$23)</f>
@@ -14305,7 +14486,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0</v>
@@ -14322,7 +14503,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="40" t="n">
@@ -14371,10 +14552,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">Blocchi!$Q$55</f>
@@ -14415,10 +14596,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">Blocchi!$Q$64</f>
@@ -14463,10 +14644,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">Blocchi!$Q$73</f>
@@ -14511,10 +14692,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">Blocchi!$Q$82</f>
@@ -14559,10 +14740,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">Blocchi!$Q$91</f>
@@ -14607,7 +14788,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="C22" s="15" t="n">
         <f aca="false">(Input!$B$23-Input!$B$24)*Tassi!$C$29</f>
@@ -14620,7 +14801,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>0</v>
@@ -14631,7 +14812,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="K24" s="15" t="n">
         <v>0</v>
@@ -14648,7 +14829,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="40" t="n">
@@ -14697,10 +14878,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">Blocchi!$Q$100</f>
@@ -14745,10 +14926,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">Blocchi!$Q$110</f>
@@ -14797,10 +14978,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C30" s="10" t="n">
         <f aca="false">Blocchi!$Q$120</f>
@@ -14849,10 +15030,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">Blocchi!$Q$130</f>
@@ -14901,10 +15082,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">Blocchi!$Q$140</f>
@@ -14953,7 +15134,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">(Input!$B$25-Input!$B$26)*Tassi!$C$35</f>
@@ -14970,7 +15151,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C34" s="15" t="n">
         <v>0</v>
@@ -14984,7 +15165,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="K35" s="15" t="n">
         <f aca="false">(1-Probabilita!$N$14)*Input!$B$31*Input!$B$26*Tassi!$D$35</f>
@@ -15005,7 +15186,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="40" t="n">
@@ -15036,7 +15217,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C38" s="20" t="n">
         <f aca="false">C14+C25+C36</f>
@@ -15065,7 +15246,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="L39" s="15" t="n">
         <f aca="false">L14+L25+SUMPRODUCT(H28:H32,C28:C32)+C33+C34+(1-Probabilita!$O$14)*Input!$B$31*Input!$B$26*Tassi!$D$35</f>
@@ -15074,7 +15255,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -15103,7 +15284,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15122,12 +15303,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D4" s="36" t="n">
         <v>2027</v>
@@ -15180,7 +15361,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Segmenti!$H$6*Blocchi!D9+Segmenti!$H$7*Blocchi!D18+Segmenti!$H$8*Blocchi!D27+Segmenti!$H$9*Blocchi!D36+Segmenti!$H$10*Blocchi!D45-Input!$B$27</f>
@@ -15225,7 +15406,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Input!$B$9*D6</f>
@@ -15270,7 +15451,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D8" s="37" t="n">
         <v>0</v>
@@ -15314,7 +15495,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">IF(D6&lt;=0,0,MIN(D8,Input!$B$44*D6))</f>
@@ -15359,7 +15540,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D10" s="37" t="n">
         <f aca="false">IF(D6&lt;=0,D8-D6,D8-D9)</f>
@@ -15404,7 +15585,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">IF(D6&lt;=0,0,Input!$B$9*(D6-D9))</f>
@@ -15449,7 +15630,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">D11-D7</f>
@@ -15494,7 +15675,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D13" s="42" t="n">
         <f aca="false">Tassi!$D$23</f>
@@ -15539,7 +15720,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C14" s="43" t="n">
         <f aca="false">SUMPRODUCT(D12:M12,D13:M13)-Input!$B$9*M10*M13</f>
@@ -15566,7 +15747,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">Segmenti!$H$17*Blocchi!D54+Segmenti!$H$18*Blocchi!D63+Segmenti!$H$19*Blocchi!D72+Segmenti!$H$20*Blocchi!D81+Segmenti!$H$21*Blocchi!D90</f>
@@ -15611,7 +15792,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D18" s="37" t="n">
         <f aca="false">Input!$B$9*D17</f>
@@ -15656,7 +15837,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D19" s="37" t="n">
         <v>0</v>
@@ -15700,7 +15881,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">IF(D17&lt;=0,0,MIN(D19,Input!$B$44*D17))</f>
@@ -15745,7 +15926,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">IF(D17&lt;=0,D19-D17,D19-D20)</f>
@@ -15790,7 +15971,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">IF(D17&lt;=0,0,Input!$B$9*(D17-D20))</f>
@@ -15835,7 +16016,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">D22-D18</f>
@@ -15880,7 +16061,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D24" s="42" t="n">
         <f aca="false">Tassi!$D$29</f>
@@ -15925,7 +16106,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C25" s="43" t="n">
         <f aca="false">SUMPRODUCT(D23:M23,D24:M24)-Input!$B$9*M21*M24</f>
@@ -15952,7 +16133,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D28" s="37" t="n">
         <f aca="false">Segmenti!$H$28*Blocchi!D99+Segmenti!$H$29*Blocchi!D109+Segmenti!$H$30*Blocchi!D119+Segmenti!$H$31*Blocchi!D129+Segmenti!$H$32*Blocchi!D139</f>
@@ -15997,7 +16178,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D29" s="37" t="n">
         <f aca="false">Input!$B$9*D28</f>
@@ -16042,7 +16223,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D30" s="37" t="n">
         <v>0</v>
@@ -16086,7 +16267,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D31" s="37" t="n">
         <f aca="false">IF(D28&lt;=0,0,MIN(D30,Input!$B$44*D28))</f>
@@ -16131,7 +16312,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D32" s="37" t="n">
         <f aca="false">IF(D28&lt;=0,D30-D28,D30-D31)</f>
@@ -16176,7 +16357,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D33" s="37" t="n">
         <f aca="false">IF(D28&lt;=0,0,Input!$B$9*(D28-D31))</f>
@@ -16221,7 +16402,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D34" s="37" t="n">
         <f aca="false">D33-D29</f>
@@ -16266,7 +16447,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D35" s="42" t="n">
         <f aca="false">Tassi!$D$41</f>
@@ -16311,7 +16492,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C36" s="43" t="n">
         <f aca="false">SUMPRODUCT(D34:M34,D35:M35)-Input!$B$9*M32*M35</f>
@@ -16320,7 +16501,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C38" s="43" t="n">
         <f aca="false">C14+C25+C36</f>
@@ -16329,7 +16510,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -16358,7 +16539,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16377,15 +16558,15 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D4" s="36" t="n">
         <v>2027</v>
@@ -16420,7 +16601,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">Input!$B$25-Input!$B$26</f>
@@ -16469,7 +16650,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C6" s="37" t="n">
         <f aca="false">Input!$B$21-Input!$B$22+Input!$B$23-Input!$B$24</f>
@@ -16518,7 +16699,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C7" s="37" t="n">
         <f aca="false">Input!$B$48+C6+MAX(0,C5)</f>
@@ -16567,7 +16748,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C8" s="37" t="n">
         <f aca="false">MAX(0,-C5)</f>
@@ -16616,7 +16797,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C9" s="37" t="n">
         <f aca="false">MIN(C8,MAX(0,C7))</f>
@@ -16665,7 +16846,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C10" s="37" t="n">
         <f aca="false">C8-C9</f>
@@ -16714,7 +16895,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C11" s="37" t="n">
         <f aca="false">MAX(0,C7-C8)</f>
@@ -16763,7 +16944,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C12" s="37" t="n">
         <f aca="false">Input!$B$47*C9</f>
@@ -16812,7 +16993,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C13" s="42" t="n">
         <f aca="false">Tassi!$C$41</f>
@@ -16861,7 +17042,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C15" s="43" t="n">
         <f aca="false">SUMPRODUCT(C12:M12,C13:M13)</f>
@@ -16870,7 +17051,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">SUM(C8:M8)</f>
@@ -16879,7 +17060,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">SUM(C9:M9)</f>
